--- a/med-data-analysis/01/LDL_medicine.xlsx
+++ b/med-data-analysis/01/LDL_medicine.xlsx
@@ -1,20 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27425"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10110"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ynomura\Dropbox\研究関係\a_講義資料\[2024.T1-T2] 医用データ解析\図・データ\第1回\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yoshihide/chiba-u/med-data-analysis/01/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B57E9273-2035-4B24-83F7-F73861C74E85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{829D3EB8-5380-0F47-B46D-AFF74076A702}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="26010" windowHeight="20985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="15120" windowHeight="18980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$E$12</definedName>
+  </definedNames>
   <calcPr calcId="191029" concurrentCalc="0"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -36,78 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="19">
-  <si>
-    <t>カルテNo.</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>千葉 太郎</t>
-  </si>
-  <si>
-    <t>東京 花子</t>
-  </si>
-  <si>
-    <t>神奈川 桜</t>
-    <rPh sb="0" eb="1">
-      <t>コ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>岡山 菊子</t>
-  </si>
-  <si>
-    <t>山梨 次郎</t>
-  </si>
-  <si>
-    <t>長野 桃子</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>山口 百合</t>
-    <rPh sb="0" eb="1">
-      <t>コ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>宮崎 林檎</t>
-  </si>
-  <si>
-    <t>大阪 三郎</t>
-  </si>
-  <si>
-    <t>富山 四郎</t>
-  </si>
-  <si>
-    <t>氏名</t>
-    <rPh sb="0" eb="2">
-      <t>シメイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>性</t>
-    <rPh sb="0" eb="1">
-      <t>セイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>生年月日</t>
-    <rPh sb="0" eb="4">
-      <t>セイネンガッピ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>LDLコレステロール値</t>
-    <rPh sb="10" eb="11">
-      <t>チ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="7">
   <si>
     <t>A</t>
     <phoneticPr fontId="1"/>
@@ -117,20 +49,23 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>福島 吾郎</t>
-    <rPh sb="3" eb="5">
-      <t>ゴロウ</t>
-    </rPh>
+    <t>ID</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>服用薬</t>
-    <rPh sb="0" eb="2">
-      <t>フクヨウ</t>
-    </rPh>
-    <rPh sb="2" eb="3">
-      <t>クスリ</t>
-    </rPh>
+    <t>sex</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>age</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>medicine</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>LDL_C</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -138,7 +73,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -150,13 +85,6 @@
       <sz val="6"/>
       <name val="Yu Gothic"/>
       <family val="3"/>
-      <charset val="128"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="6"/>
-      <name val="Yu Gothic"/>
-      <family val="2"/>
       <charset val="128"/>
       <scheme val="minor"/>
     </font>
@@ -226,24 +154,21 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -526,259 +451,224 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F12"/>
-  <sheetFormatPr defaultRowHeight="18.75"/>
+  <dimension ref="A1:E12"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="17" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="3.5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="21.375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.83203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="18.75" customHeight="1">
+    <row r="1" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="2">
+        <v>100000</v>
+      </c>
+      <c r="B2" s="3">
+        <v>1</v>
+      </c>
+      <c r="C2" s="3">
+        <v>55</v>
+      </c>
+      <c r="D2" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" ht="18.75" customHeight="1">
-      <c r="A2" s="2">
-        <v>438519</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="4">
-        <v>1</v>
-      </c>
-      <c r="D2" s="5">
-        <v>26028</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="F2" s="6">
+      <c r="E2" s="5">
         <v>113</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="18.75" customHeight="1">
+    <row r="3" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
-        <v>483886</v>
-      </c>
-      <c r="B3" s="3" t="s">
+        <v>100001</v>
+      </c>
+      <c r="B3" s="3">
         <v>2</v>
       </c>
-      <c r="C3" s="4">
+      <c r="C3" s="3">
+        <v>57</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="E3" s="5">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="2">
+        <v>100002</v>
+      </c>
+      <c r="B4" s="3">
         <v>2</v>
       </c>
-      <c r="D3" s="5">
-        <v>24959</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="F3" s="6">
+      <c r="C4" s="3">
+        <v>47</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="E4" s="5">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="2">
+        <v>100003</v>
+      </c>
+      <c r="B5" s="3">
+        <v>1</v>
+      </c>
+      <c r="C5" s="3">
+        <v>57</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="E5" s="5">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="2">
+        <v>100004</v>
+      </c>
+      <c r="B6" s="3">
+        <v>2</v>
+      </c>
+      <c r="C6" s="3">
+        <v>50</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="E6" s="5">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="2">
+        <v>100005</v>
+      </c>
+      <c r="B7" s="3">
+        <v>2</v>
+      </c>
+      <c r="C7" s="3">
+        <v>77</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="E7" s="5">
         <v>125</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="18.75" customHeight="1">
-      <c r="A4" s="2">
-        <v>155082</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="C4" s="4">
+    <row r="8" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="2">
+        <v>100006</v>
+      </c>
+      <c r="B8" s="3">
+        <v>1</v>
+      </c>
+      <c r="C8" s="3">
+        <v>67</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="E8" s="5">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="2">
+        <v>100007</v>
+      </c>
+      <c r="B9" s="3">
         <v>2</v>
       </c>
-      <c r="D4" s="5">
-        <v>28654</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="F4" s="6">
+      <c r="C9" s="3">
+        <v>55</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="E9" s="5">
         <v>120</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="18.75" customHeight="1">
-      <c r="A5" s="2">
-        <v>471732</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C5" s="4">
-        <v>1</v>
-      </c>
-      <c r="D5" s="5">
-        <v>25075</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="F5" s="6">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="18.75" customHeight="1">
-      <c r="A6" s="2">
-        <v>462262</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="C6" s="4">
+    <row r="10" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="2">
+        <v>100008</v>
+      </c>
+      <c r="B10" s="3">
+        <v>1</v>
+      </c>
+      <c r="C10" s="3">
+        <v>69</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="E10" s="5">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="2">
+        <v>100009</v>
+      </c>
+      <c r="B11" s="3">
+        <v>1</v>
+      </c>
+      <c r="C11" s="3">
+        <v>55</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="E11" s="5">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="19" x14ac:dyDescent="0.25">
+      <c r="A12" s="2">
+        <v>100010</v>
+      </c>
+      <c r="B12" s="3">
         <v>2</v>
       </c>
-      <c r="D6" s="5">
-        <v>27596</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="F6" s="6">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" ht="18.75" customHeight="1">
-      <c r="A7" s="2">
-        <v>376238</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C7" s="4">
-        <v>2</v>
-      </c>
-      <c r="D7" s="5">
-        <v>17785</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="F7" s="6">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" ht="18.75" customHeight="1">
-      <c r="A8" s="2">
-        <v>461429</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C8" s="4">
-        <v>1</v>
-      </c>
-      <c r="D8" s="5">
-        <v>21519</v>
-      </c>
-      <c r="E8" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="F8" s="6">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" ht="18.75" customHeight="1">
-      <c r="A9" s="2">
-        <v>488384</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C9" s="4">
-        <v>2</v>
-      </c>
-      <c r="D9" s="5">
-        <v>25851</v>
-      </c>
-      <c r="E9" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="F9" s="6">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" ht="18.75" customHeight="1">
-      <c r="A10" s="2">
-        <v>398036</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="4">
-        <v>1</v>
-      </c>
-      <c r="D10" s="5">
-        <v>20797</v>
-      </c>
-      <c r="E10" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="F10" s="6">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" ht="18.75" customHeight="1">
-      <c r="A11" s="2">
-        <v>442028</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C11" s="4">
-        <v>1</v>
-      </c>
-      <c r="D11" s="5">
-        <v>25957</v>
-      </c>
-      <c r="E11" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="F11" s="6">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" ht="19.5">
-      <c r="A12" s="2">
-        <v>398036</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C12" s="4">
-        <v>2</v>
-      </c>
-      <c r="D12" s="5">
-        <v>20797</v>
-      </c>
-      <c r="E12" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="F12" s="6">
+      <c r="C12" s="3">
+        <v>69</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="E12" s="5">
         <v>113</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:E12" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>